--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_TRAUMACOR CULLEREDO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_TRAUMACOR CULLEREDO.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>59.6889</v>
+        <v>78.7283</v>
       </c>
       <c r="E2" t="n">
-        <v>64.22150000000001</v>
+        <v>76.3398</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.5331</v>
+        <v>2.3887</v>
       </c>
       <c r="G2" t="n">
         <v>30.7033</v>
@@ -610,13 +610,13 @@
         <v>59.5378</v>
       </c>
       <c r="S2" t="n">
-        <v>-21.4242</v>
+        <v>-2.3846</v>
       </c>
       <c r="T2" t="n">
-        <v>-15.1193</v>
+        <v>-3.0013</v>
       </c>
       <c r="U2" t="n">
-        <v>-6.3046</v>
+        <v>0.6169000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>38.4629</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. FALL</t>
+          <t>D. WILLIAM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>43.7941</v>
+        <v>30.6977</v>
       </c>
       <c r="E3" t="n">
-        <v>21.4068</v>
+        <v>22.1852</v>
       </c>
       <c r="F3" t="n">
-        <v>22.3877</v>
+        <v>8.512499999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>23.8379</v>
+        <v>13.9619</v>
       </c>
       <c r="H3" t="n">
-        <v>14.9882</v>
+        <v>8.5044</v>
       </c>
       <c r="I3" t="n">
-        <v>8.8498</v>
+        <v>5.458</v>
       </c>
       <c r="J3" t="n">
-        <v>64.599</v>
+        <v>49.089</v>
       </c>
       <c r="K3" t="n">
-        <v>40.3634</v>
+        <v>34.0763</v>
       </c>
       <c r="L3" t="n">
-        <v>24.2361</v>
+        <v>15.0131</v>
       </c>
       <c r="M3" t="n">
-        <v>-40.7614</v>
+        <v>-35.1272</v>
       </c>
       <c r="N3" t="n">
-        <v>-25.3754</v>
+        <v>-25.5724</v>
       </c>
       <c r="O3" t="n">
-        <v>-15.386</v>
+        <v>-9.555099999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>-47.0034</v>
+        <v>5.8756</v>
       </c>
       <c r="Q3" t="n">
-        <v>-101.8412</v>
+        <v>-56.4041</v>
       </c>
       <c r="R3" t="n">
-        <v>54.8374</v>
+        <v>62.2796</v>
       </c>
       <c r="S3" t="n">
-        <v>61.17</v>
+        <v>5.8239</v>
       </c>
       <c r="T3" t="n">
-        <v>35.9043</v>
+        <v>1.1462</v>
       </c>
       <c r="U3" t="n">
-        <v>25.2657</v>
+        <v>4.6776</v>
       </c>
       <c r="V3" t="n">
-        <v>5.790100000000002</v>
+        <v>5.036499999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>22.7451</v>
+        <v>28.3548</v>
       </c>
       <c r="X3" t="n">
-        <v>-16.955</v>
+        <v>-23.3185</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. WILLIAM</t>
+          <t>A. CORBACHO DE LA CRUZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>31.3248</v>
+        <v>26.5478</v>
       </c>
       <c r="E4" t="n">
-        <v>24.1798</v>
+        <v>7.740900000000002</v>
       </c>
       <c r="F4" t="n">
-        <v>7.145299999999999</v>
+        <v>18.807</v>
       </c>
       <c r="G4" t="n">
-        <v>13.9619</v>
+        <v>-1.619700000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>8.5044</v>
+        <v>-6.184</v>
       </c>
       <c r="I4" t="n">
-        <v>5.458</v>
+        <v>4.564300000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>49.089</v>
+        <v>17.0713</v>
       </c>
       <c r="K4" t="n">
-        <v>34.0763</v>
+        <v>8.3972</v>
       </c>
       <c r="L4" t="n">
-        <v>15.0131</v>
+        <v>8.674099999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-35.1272</v>
+        <v>-18.6911</v>
       </c>
       <c r="N4" t="n">
-        <v>-25.5724</v>
+        <v>-14.5814</v>
       </c>
       <c r="O4" t="n">
-        <v>-9.555099999999999</v>
+        <v>-4.1095</v>
       </c>
       <c r="P4" t="n">
-        <v>5.8756</v>
+        <v>25.2641</v>
       </c>
       <c r="Q4" t="n">
-        <v>-56.4041</v>
+        <v>-15.6675</v>
       </c>
       <c r="R4" t="n">
-        <v>62.2796</v>
+        <v>40.932</v>
       </c>
       <c r="S4" t="n">
-        <v>6.451099999999999</v>
+        <v>0.4470999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>3.140599999999999</v>
+        <v>-3.2229</v>
       </c>
       <c r="U4" t="n">
-        <v>3.3109</v>
+        <v>3.6695</v>
       </c>
       <c r="V4" t="n">
-        <v>5.036499999999999</v>
+        <v>2.4562</v>
       </c>
       <c r="W4" t="n">
-        <v>28.3548</v>
+        <v>9.5602</v>
       </c>
       <c r="X4" t="n">
-        <v>-23.3185</v>
+        <v>-7.103999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. CORBACHO DE LA CRUZ</t>
+          <t>K. FALL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>13.8569</v>
+        <v>7.293099999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-5.037799999999999</v>
+        <v>-4.210500000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>18.8944</v>
+        <v>11.5038</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.619700000000001</v>
+        <v>23.8379</v>
       </c>
       <c r="H5" t="n">
-        <v>-6.184</v>
+        <v>14.9882</v>
       </c>
       <c r="I5" t="n">
-        <v>4.564300000000001</v>
+        <v>8.8498</v>
       </c>
       <c r="J5" t="n">
-        <v>17.0713</v>
+        <v>64.599</v>
       </c>
       <c r="K5" t="n">
-        <v>8.3972</v>
+        <v>40.3634</v>
       </c>
       <c r="L5" t="n">
-        <v>8.674099999999999</v>
+        <v>24.2361</v>
       </c>
       <c r="M5" t="n">
-        <v>-18.6911</v>
+        <v>-40.7614</v>
       </c>
       <c r="N5" t="n">
-        <v>-14.5814</v>
+        <v>-25.3754</v>
       </c>
       <c r="O5" t="n">
-        <v>-4.1095</v>
+        <v>-15.386</v>
       </c>
       <c r="P5" t="n">
-        <v>25.2641</v>
+        <v>-47.0034</v>
       </c>
       <c r="Q5" t="n">
-        <v>-15.6675</v>
+        <v>-101.8412</v>
       </c>
       <c r="R5" t="n">
-        <v>40.932</v>
+        <v>54.8374</v>
       </c>
       <c r="S5" t="n">
-        <v>-12.2442</v>
+        <v>24.6687</v>
       </c>
       <c r="T5" t="n">
-        <v>-16.0005</v>
+        <v>10.2867</v>
       </c>
       <c r="U5" t="n">
-        <v>3.7567</v>
+        <v>14.3819</v>
       </c>
       <c r="V5" t="n">
-        <v>2.4562</v>
+        <v>5.790100000000002</v>
       </c>
       <c r="W5" t="n">
-        <v>9.5602</v>
+        <v>22.7451</v>
       </c>
       <c r="X5" t="n">
-        <v>-7.103999999999999</v>
+        <v>-16.955</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. SANJURJO BOTEJARA</t>
+          <t>J. FERNANDEZ GARCIA-GARABAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.082699999999998</v>
+        <v>1.1316</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.920000000000001</v>
+        <v>1.7204</v>
       </c>
       <c r="F6" t="n">
-        <v>4.0028</v>
+        <v>-0.5888</v>
       </c>
       <c r="G6" t="n">
-        <v>1.730199999999999</v>
+        <v>0.5987</v>
       </c>
       <c r="H6" t="n">
-        <v>-6.559699999999999</v>
+        <v>0.2502</v>
       </c>
       <c r="I6" t="n">
-        <v>8.290099999999999</v>
+        <v>0.3485</v>
       </c>
       <c r="J6" t="n">
-        <v>13.8305</v>
+        <v>1.8685</v>
       </c>
       <c r="K6" t="n">
-        <v>8.475399999999999</v>
+        <v>0.4491</v>
       </c>
       <c r="L6" t="n">
-        <v>5.3553</v>
+        <v>1.4193</v>
       </c>
       <c r="M6" t="n">
-        <v>-12.1004</v>
+        <v>-1.2698</v>
       </c>
       <c r="N6" t="n">
-        <v>-15.0353</v>
+        <v>-0.199</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9352</v>
+        <v>-1.0708</v>
       </c>
       <c r="P6" t="n">
-        <v>-14.4926</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q6" t="n">
-        <v>-39.7569</v>
+        <v>-0.9792</v>
       </c>
       <c r="R6" t="n">
-        <v>25.2639</v>
+        <v>0.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>10.8948</v>
+        <v>0.5121</v>
       </c>
       <c r="T6" t="n">
-        <v>8.0421</v>
+        <v>0.5558</v>
       </c>
       <c r="U6" t="n">
-        <v>2.8525</v>
+        <v>-0.0437</v>
       </c>
       <c r="V6" t="n">
-        <v>2.9505</v>
+        <v>0.6083</v>
       </c>
       <c r="W6" t="n">
-        <v>14.9649</v>
+        <v>0.2754</v>
       </c>
       <c r="X6" t="n">
-        <v>-12.0145</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ GARCIA-GARABAL</t>
+          <t>M. LAGE MARCOTE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4771</v>
+        <v>0.2356</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4134</v>
+        <v>-0.0546</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9363</v>
+        <v>0.2901</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5987</v>
+        <v>0.2829</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2502</v>
+        <v>-0.5458</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3485</v>
+        <v>0.8287</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8685</v>
+        <v>0.0048</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4491</v>
+        <v>-0.6822</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4193</v>
+        <v>0.6871</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2698</v>
+        <v>0.2781</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.199</v>
+        <v>0.1364</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0708</v>
+        <v>0.1416</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5875</v>
+        <v>0.1958</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3917</v>
+        <v>0.1958</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1424</v>
+        <v>-0.2432</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2488</v>
+        <v>-0.0594</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3912</v>
+        <v>-0.1838</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6083</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1956</v>
+        <v>0.191</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7813</v>
+        <v>0.8835999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5857</v>
+        <v>-0.6927</v>
       </c>
       <c r="G8" t="n">
         <v>0.2252</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0295</v>
+        <v>-0.03409999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1782</v>
+        <v>-0.0759</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1487</v>
+        <v>0.0418</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. LAGE MARCOTE</t>
+          <t>G. CARBALLIDO PUÑAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1821</v>
+        <v>-0.5597</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0546</v>
+        <v>-0.5514</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2367</v>
+        <v>-0.0083</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2829</v>
+        <v>-0.5597</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5458</v>
+        <v>-0.5597</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8287</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0048</v>
+        <v>-0.3556</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6822</v>
+        <v>-0.3556</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6871</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2781</v>
+        <v>-0.2042</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1364</v>
+        <v>-0.2042</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1416</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.1958</v>
       </c>
       <c r="R9" t="n">
         <v>0.1958</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2967</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0594</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2373</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. CARBALLIDO PUÑAL</t>
+          <t>A. LOIRA PINHEIRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5597</v>
+        <v>-2.5326</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5514</v>
+        <v>-0.3449</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0083</v>
+        <v>-2.1876</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5597</v>
+        <v>-1.4805</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5597</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-0.8691</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3556</v>
+        <v>-0.6014</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3556</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.6014</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2042</v>
+        <v>-0.8792</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2042</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0.2678</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1958</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1958</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.1646</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.2564</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0.09179999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. LOIRA PINHEIRO</t>
+          <t>M. IGLESIAS VALDERRAMA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3887</v>
+        <v>-3.3394</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.03790000000000004</v>
+        <v>-3.0605</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3508</v>
+        <v>-0.2791</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4805</v>
+        <v>-4.1752</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-2.1201</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8691</v>
+        <v>-2.0552</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6014</v>
+        <v>-0.8545</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.8641000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6014</v>
+        <v>-1.7186</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8792</v>
+        <v>-3.3208</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-2.9842</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2678</v>
+        <v>-0.3366</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.1543</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.9584</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>4.1127</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3084</v>
+        <v>-0.5976000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5634</v>
+        <v>-0.1324</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.255</v>
+        <v>-0.4652</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2166</v>
+        <v>-0.721</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.1151000000000001</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2166</v>
+        <v>-0.6058</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. IGLESIAS VALDERRAMA</t>
+          <t>J. MARTINEZ FERREIRO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6676</v>
+        <v>-3.798899999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2815</v>
+        <v>-2.6474</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3858999999999999</v>
+        <v>-1.1514</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.1752</v>
+        <v>-0.4042999999999991</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.1201</v>
+        <v>-6.7978</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.0552</v>
+        <v>6.393799999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8545</v>
+        <v>11.1529</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8641000000000001</v>
+        <v>2.9512</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.7186</v>
+        <v>8.201699999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.3208</v>
+        <v>-11.5571</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.9842</v>
+        <v>-9.749699999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3366</v>
+        <v>-1.8081</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1543</v>
+        <v>3.1333</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9584</v>
+        <v>-14.6883</v>
       </c>
       <c r="R12" t="n">
-        <v>4.1127</v>
+        <v>17.8217</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9256</v>
+        <v>-0.3444000000000002</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3534999999999999</v>
+        <v>0.1198</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5722</v>
+        <v>-0.4646</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.721</v>
+        <v>-6.1833</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.1151000000000001</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6058</v>
+        <v>-6.9519</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X. IGOA ENDJILO</t>
+          <t>P. SANJURJO BOTEJARA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.487900000000001</v>
+        <v>-5.3202</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.5351</v>
+        <v>-7.2811</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9528000000000001</v>
+        <v>1.961000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.9659</v>
+        <v>1.730199999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.0623</v>
+        <v>-6.559699999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.09630000000000008</v>
+        <v>8.290099999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4284000000000001</v>
+        <v>13.8305</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4833</v>
+        <v>8.475399999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05479999999999999</v>
+        <v>5.3553</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.5375</v>
+        <v>-12.1004</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.5791</v>
+        <v>-15.0353</v>
       </c>
       <c r="O13" t="n">
-        <v>0.04150000000000001</v>
+        <v>2.9352</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9791999999999998</v>
+        <v>-14.4926</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.8962</v>
+        <v>-39.7569</v>
       </c>
       <c r="R13" t="n">
-        <v>3.9169</v>
+        <v>25.2639</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1163</v>
+        <v>4.4922</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1811</v>
+        <v>3.681</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2974</v>
+        <v>0.8109999999999997</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.4265</v>
+        <v>2.9505</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6083</v>
+        <v>14.9649</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0348</v>
+        <v>-12.0145</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. MARTINEZ FERREIRO</t>
+          <t>X. IGOA ENDJILO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.2991</v>
+        <v>-5.753</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.3676</v>
+        <v>-4.9876</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.9315</v>
+        <v>-0.7654999999999998</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4042999999999991</v>
+        <v>-2.9659</v>
       </c>
       <c r="H14" t="n">
-        <v>-6.7978</v>
+        <v>-3.0623</v>
       </c>
       <c r="I14" t="n">
-        <v>6.393799999999999</v>
+        <v>0.09630000000000008</v>
       </c>
       <c r="J14" t="n">
-        <v>11.1529</v>
+        <v>-0.4284000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9512</v>
+        <v>-0.4833</v>
       </c>
       <c r="L14" t="n">
-        <v>8.201699999999999</v>
+        <v>0.05479999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-11.5571</v>
+        <v>-2.5375</v>
       </c>
       <c r="N14" t="n">
-        <v>-9.749699999999999</v>
+        <v>-2.5791</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.8081</v>
+        <v>0.04150000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>3.1333</v>
+        <v>-0.9791999999999998</v>
       </c>
       <c r="Q14" t="n">
-        <v>-14.6883</v>
+        <v>-4.8962</v>
       </c>
       <c r="R14" t="n">
-        <v>17.8217</v>
+        <v>3.9169</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.8454</v>
+        <v>-1.3813</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.6004</v>
+        <v>-0.2712</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.244899999999999</v>
+        <v>-1.1102</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.1833</v>
+        <v>-0.4265</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7685999999999999</v>
+        <v>0.6083</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.9519</v>
+        <v>-1.0348</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>-15.4896</v>
+        <v>-6.480200000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-15.3191</v>
+        <v>-10.7075</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1702999999999999</v>
+        <v>4.227599999999999</v>
       </c>
       <c r="G15" t="n">
         <v>11.6768</v>
@@ -1624,13 +1624,13 @@
         <v>24.4806</v>
       </c>
       <c r="S15" t="n">
-        <v>-7.966</v>
+        <v>1.0433</v>
       </c>
       <c r="T15" t="n">
-        <v>-4.5651</v>
+        <v>0.04640000000000005</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.4008</v>
+        <v>0.9970000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>-6.666399999999999</v>
@@ -1657,13 +1657,13 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-31.1069</v>
+        <v>-28.1367</v>
       </c>
       <c r="E16" t="n">
-        <v>-28.4535</v>
+        <v>-24.8587</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.653</v>
+        <v>-3.2779</v>
       </c>
       <c r="G16" t="n">
         <v>-26.4241</v>
@@ -1702,13 +1702,13 @@
         <v>31.1394</v>
       </c>
       <c r="S16" t="n">
-        <v>-5.5497</v>
+        <v>-2.5799</v>
       </c>
       <c r="T16" t="n">
-        <v>-5.4651</v>
+        <v>-1.8705</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.08470000000000005</v>
+        <v>-0.7097</v>
       </c>
       <c r="V16" t="n">
         <v>9.680200000000001</v>
@@ -1735,13 +1735,13 @@
         <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>-41.6443</v>
+        <v>-30.7679</v>
       </c>
       <c r="E17" t="n">
-        <v>-15.7414</v>
+        <v>-10.1529</v>
       </c>
       <c r="F17" t="n">
-        <v>-25.9031</v>
+        <v>-20.6147</v>
       </c>
       <c r="G17" t="n">
         <v>3.970999999999999</v>
@@ -1780,13 +1780,13 @@
         <v>41.1277</v>
       </c>
       <c r="S17" t="n">
-        <v>-14.1918</v>
+        <v>-3.3147</v>
       </c>
       <c r="T17" t="n">
-        <v>-7.424</v>
+        <v>-1.8359</v>
       </c>
       <c r="U17" t="n">
-        <v>-6.7675</v>
+        <v>-1.4793</v>
       </c>
       <c r="V17" t="n">
         <v>-9.488799999999999</v>
@@ -1813,22 +1813,22 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>39.95840000000001</v>
+        <v>58.1365</v>
       </c>
       <c r="E18" t="n">
-        <v>30.7029</v>
+        <v>40.01280000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>9.2561</v>
+        <v>18.1247</v>
       </c>
       <c r="G18" t="n">
         <v>49.35850000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-44.4595</v>
+        <v>-44.45950000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>93.8186</v>
+        <v>93.81859999999999</v>
       </c>
       <c r="J18" t="n">
         <v>275.7584</v>
@@ -1855,16 +1855,16 @@
         <v>-424.0095</v>
       </c>
       <c r="R18" t="n">
-        <v>366.233</v>
+        <v>366.2330000000001</v>
       </c>
       <c r="S18" t="n">
-        <v>8.092500000000001</v>
+        <v>26.2721</v>
       </c>
       <c r="T18" t="n">
-        <v>-3.685200000000005</v>
+        <v>5.622800000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>11.7789</v>
+        <v>20.6474</v>
       </c>
       <c r="V18" t="n">
         <v>40.2821</v>
